--- a/motion_mecro_qd77_result2.xlsx
+++ b/motion_mecro_qd77_result2.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>XB0</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>XB0</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Y14</t>
+          <t>YA4</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>U1\G4300</t>
+          <t>UA\G4300</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>U1\G4300</t>
+          <t>UA\G4300</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>U1\G6001</t>
+          <t>UA\G6001</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>U1\G12</t>
+          <t>UA\G12</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>U1\G14</t>
+          <t>UA\G14</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>U1\G6004</t>
+          <t>UA\G6004</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>U1\G6004</t>
+          <t>UA\G6004</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>U1\G10</t>
+          <t>UA\G10</t>
         </is>
       </c>
     </row>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Y20</t>
+          <t>YB0</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Y20</t>
+          <t>YB0</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Y18</t>
+          <t>YA8</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Y19</t>
+          <t>YA9</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>U1\G6006</t>
+          <t>UA\G6006</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>U1\G4351</t>
+          <t>UA\G4351</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>U1\G4351</t>
+          <t>UA\G4351</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>U1\G48</t>
+          <t>UA\G48</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>U1\G30101</t>
+          <t>UA\G30101</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>U1\G30102</t>
+          <t>UA\G30102</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>U1\G30100</t>
+          <t>UA\G30100</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>U1\G4302</t>
+          <t>UA\G4302</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>U1\G1551</t>
+          <t>UA\G1551</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>U1\G1551</t>
+          <t>UA\G1551</t>
         </is>
       </c>
     </row>

--- a/motion_mecro_qd77_result2.xlsx
+++ b/motion_mecro_qd77_result2.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E749"/>
+  <dimension ref="A1:E1496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14245,7 +14245,7815 @@
       </c>
     </row>
     <row r="749">
-      <c r="C749" t="inlineStr">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>ZR60202.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>D17040.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>ZR60202.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>D17040.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>ZR60202.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>D17040.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>ZR60203.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>SM401</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>ZR60203.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>D17040.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>ZR60203.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>D17040.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>ZR60402.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>D17040.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>XB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>XB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>LDP</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>M17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>T17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>M17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>T17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="C794" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>K30</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>M17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>SM412</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>D17048.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>M17040</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>D17041.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>M601</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>M17045</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>D17048.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>M17042</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>D17040.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>LDP</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>D17040.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>D17040.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>POSITION_INTERLOCK</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>M17045</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>D17042.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>D17044.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>D17042.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>D17042.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>D17042.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>D17042.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>D17042.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>D17042.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>D17042.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>D17042.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>D17042.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>D17042.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>D17042.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>D17042.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>D17042.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>D17042.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>D17042.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>D17042.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>D17044.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>D17044.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>D17044.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>D17044.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>D17044.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>D17044.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>D17044.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>D17044.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>D17044.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>D17044.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>D17044.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>D17044.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>D17044.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>D17044.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>D17044.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>D17044.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>POSITION_BIT</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>M17042</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>D17044.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>D17046.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>D17042.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>D17044.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>D17046.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>D17042.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>D17044.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>D17046.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>D17042.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>D17044.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>D17046.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>D17042.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>D17044.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>D17046.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>D17042.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>D17044.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>D17046.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>D17042.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>D17044.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>D17046.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>D17042.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>D17044.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>D17046.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>D17042.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>D17044.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>D17046.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>D17042.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>D17044.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>D17046.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>D17042.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>D17044.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>D17046.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>D17042.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>D17044.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>D17046.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>D17042.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>D17044.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>D17046.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>D17042.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>D17044.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>D17046.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>D17042.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>D17044.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>D17046.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>D17042.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>LDI</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>D17044.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>D17046.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>AND&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="C997" t="inlineStr"/>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>D17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>M17044</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>YA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>D17040.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>M17045</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>M17044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>M17045</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>POSITION_START</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>D17059.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>D17059.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="C1019" t="inlineStr"/>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>M17044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>D17046.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>K9001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="C1025" t="inlineStr"/>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>D17046.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>K9001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="C1036" t="inlineStr"/>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>D17046.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="C1040" t="inlineStr"/>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>D17046.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="C1044" t="inlineStr"/>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>D17046.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="C1048" t="inlineStr"/>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>D17046.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="C1052" t="inlineStr"/>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>D17046.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="C1056" t="inlineStr"/>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>D17046.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="C1060" t="inlineStr"/>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>D17046.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="C1064" t="inlineStr"/>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>D17046.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="C1068" t="inlineStr"/>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>D17046.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="C1072" t="inlineStr"/>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>D17046.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="C1076" t="inlineStr"/>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>D17046.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="C1080" t="inlineStr"/>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>D17046.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="C1084" t="inlineStr"/>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>D17046.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="C1088" t="inlineStr"/>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>D17046.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="C1092" t="inlineStr"/>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>M17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>D17046.F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>K15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="C1096" t="inlineStr"/>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>POSITION_MOVEMENT</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>LD&lt;</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="C1099" t="inlineStr"/>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>D17046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>OR&lt;</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="C1101" t="inlineStr"/>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>D17047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>AND&lt;=</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="C1103" t="inlineStr"/>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>M17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="C1107" t="inlineStr"/>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>ZR76040</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="C1109" t="inlineStr"/>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>ZR76042</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="C1111" t="inlineStr"/>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>ZR76044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="C1113" t="inlineStr"/>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>ZR76046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="C1115" t="inlineStr"/>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>ZR76048</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="C1117" t="inlineStr"/>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>ZR76050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="C1119" t="inlineStr"/>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>ZR76052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="C1121" t="inlineStr"/>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>ZR76054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="C1123" t="inlineStr"/>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>ZR76056</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="C1125" t="inlineStr"/>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>ZR76058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="C1127" t="inlineStr"/>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>ZR76060</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="C1129" t="inlineStr"/>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>ZR76062</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="C1131" t="inlineStr"/>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>ZR76064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="C1133" t="inlineStr"/>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>ZR76066</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="C1135" t="inlineStr"/>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>ZR76068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="C1138" t="inlineStr"/>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>ZR79040</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="C1140" t="inlineStr"/>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>ZR79042</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="C1142" t="inlineStr"/>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>ZR79044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="C1144" t="inlineStr"/>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>ZR79046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="C1146" t="inlineStr"/>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>ZR79048</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="C1148" t="inlineStr"/>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>ZR79050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="C1150" t="inlineStr"/>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>ZR79052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="C1152" t="inlineStr"/>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>ZR79054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="C1154" t="inlineStr"/>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>ZR79056</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="C1156" t="inlineStr"/>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>ZR79058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="C1158" t="inlineStr"/>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>ZR79060</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="C1160" t="inlineStr"/>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>ZR79062</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="C1162" t="inlineStr"/>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>ZR79064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="C1164" t="inlineStr"/>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>ZR79066</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="C1166" t="inlineStr"/>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>ZR79068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="C1169" t="inlineStr"/>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>ZR82040</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="C1171" t="inlineStr"/>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>ZR82042</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="C1173" t="inlineStr"/>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>ZR82044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="C1175" t="inlineStr"/>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>ZR82046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="C1177" t="inlineStr"/>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>ZR82048</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="C1179" t="inlineStr"/>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>ZR82050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="C1181" t="inlineStr"/>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>ZR82052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="C1183" t="inlineStr"/>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>ZR82054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="C1185" t="inlineStr"/>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>ZR82056</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="C1187" t="inlineStr"/>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>ZR82058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="C1189" t="inlineStr"/>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>ZR82060</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="C1191" t="inlineStr"/>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>ZR82062</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="C1193" t="inlineStr"/>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>ZR82064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="C1195" t="inlineStr"/>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>ZR82066</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="C1197" t="inlineStr"/>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>ZR82068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>M17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr"/>
+    </row>
+    <row r="1201">
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>K9001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="C1204" t="inlineStr"/>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>UA\G4500</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="C1208" t="inlineStr"/>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>UA\G4500</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="C1210" t="inlineStr"/>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="C1211" t="inlineStr"/>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="C1213" t="inlineStr"/>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="C1214" t="inlineStr"/>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="C1216" t="inlineStr"/>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>UA\G8001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>SM400</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>ZR62002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="C1220" t="inlineStr"/>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>UA\G162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>ZR62202</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="C1222" t="inlineStr"/>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>UA\G164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>SM400</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>D*</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>ZR61602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="C1228" t="inlineStr"/>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>ZR180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="C1229" t="inlineStr"/>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>ZR186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>D*</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>ZR88040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="C1233" t="inlineStr"/>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>ZR180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="C1234" t="inlineStr"/>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>ZR186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>SM400</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>ZR186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="C1238" t="inlineStr"/>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>UA\G8004</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>UA\G8004</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="C1240" t="inlineStr"/>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>UA\G160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>ZR70040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="C1244" t="inlineStr"/>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>ZR73040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="C1245" t="inlineStr"/>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="C1247" t="inlineStr"/>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>ZR76040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="C1248" t="inlineStr"/>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="C1250" t="inlineStr"/>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>ZR79040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="C1251" t="inlineStr"/>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="C1253" t="inlineStr"/>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>ZR82040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="C1254" t="inlineStr"/>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>ZR85040Z4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="C1256" t="inlineStr"/>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>M17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>LDD&lt;</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>ZR63002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="C1263" t="inlineStr"/>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>ORD&gt;</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>ZR63202</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="C1265" t="inlineStr"/>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>M17051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr"/>
+    </row>
+    <row r="1269">
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>M17051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>YB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>M17051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr"/>
+    </row>
+    <row r="1278">
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>M17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>M17047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr"/>
+    </row>
+    <row r="1285">
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>D17051.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>YB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>YAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>YAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr"/>
+    </row>
+    <row r="1295">
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="C1296" t="inlineStr"/>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr"/>
+    </row>
+    <row r="1298">
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr"/>
+    </row>
+    <row r="1300">
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>M17047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>D17050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="C1302" t="inlineStr"/>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>POSITION_CHECK</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="C1306" t="inlineStr"/>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="C1307" t="inlineStr"/>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>D800</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>D-</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="C1309" t="inlineStr"/>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="C1310" t="inlineStr"/>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>D802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>ZR60002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="C1312" t="inlineStr"/>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>ANDD&lt;=</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>ZR60002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="C1314" t="inlineStr"/>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>D800</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>ANDD&gt;=</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>ZR60002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="C1316" t="inlineStr"/>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>D802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>UA\G8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="C1318" t="inlineStr"/>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>M17047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>M17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>D17040.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>D17040.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr"/>
+    </row>
+    <row r="1325">
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="C1326" t="inlineStr"/>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="C1328" t="inlineStr"/>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>ZR85040</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>D17056.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="C1332" t="inlineStr"/>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="C1334" t="inlineStr"/>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>ZR85042</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>D17056.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="C1338" t="inlineStr"/>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="C1340" t="inlineStr"/>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>ZR85044</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>D17056.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="C1344" t="inlineStr"/>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="C1346" t="inlineStr"/>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>ZR85046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>D17056.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="C1350" t="inlineStr"/>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="C1352" t="inlineStr"/>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>ZR85048</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>D17056.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="C1356" t="inlineStr"/>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="C1358" t="inlineStr"/>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>ZR85050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>D17056.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="C1362" t="inlineStr"/>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="C1364" t="inlineStr"/>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>ZR85052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>D17056.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="C1368" t="inlineStr"/>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="C1370" t="inlineStr"/>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>ZR85054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>D17056.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="C1374" t="inlineStr"/>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="C1376" t="inlineStr"/>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>ZR85056</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>D17056.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="C1380" t="inlineStr"/>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="C1382" t="inlineStr"/>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>ZR85058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>D17056.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr"/>
+    </row>
+    <row r="1385">
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="C1386" t="inlineStr"/>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="C1388" t="inlineStr"/>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>ZR85060</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>D17056.A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="C1392" t="inlineStr"/>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="C1394" t="inlineStr"/>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>ZR85062</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>D17056.B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="C1398" t="inlineStr"/>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="C1400" t="inlineStr"/>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>ZR85064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>D17056.C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="C1404" t="inlineStr"/>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="C1406" t="inlineStr"/>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>ZR85066</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>D17056.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr"/>
+    </row>
+    <row r="1409">
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>D17052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="C1410" t="inlineStr"/>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>K15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>D17054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="C1412" t="inlineStr"/>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>ZR85068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>D17056.E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>MANUAL_COMMAND</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr"/>
+    </row>
+    <row r="1415">
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr"/>
+    </row>
+    <row r="1417">
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>D17058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="C1418" t="inlineStr"/>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>D*</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>ZR62402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="C1420" t="inlineStr"/>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>ZR190</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="C1421" t="inlineStr"/>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>ZR192</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr"/>
+    </row>
+    <row r="1423">
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>D17058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="C1424" t="inlineStr"/>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>D*</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>ZR62602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="C1426" t="inlineStr"/>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>ZR190</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="C1427" t="inlineStr"/>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>ZR192</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr"/>
+    </row>
+    <row r="1429">
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>AND=</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>D17058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="C1430" t="inlineStr"/>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>D*</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>ZR62802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="C1432" t="inlineStr"/>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>ZR190</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="C1433" t="inlineStr"/>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>ZR192</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr"/>
+    </row>
+    <row r="1435">
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>ZR192</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="C1436" t="inlineStr"/>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>UA\G4451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>DMOV</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>UA\G4451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="C1438" t="inlineStr"/>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>UA\G198</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr"/>
+    </row>
+    <row r="1441">
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr"/>
+    </row>
+    <row r="1443">
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>D17059.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr"/>
+    </row>
+    <row r="1445">
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr"/>
+    </row>
+    <row r="1447">
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>D17059.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr"/>
+    </row>
+    <row r="1449">
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr"/>
+    </row>
+    <row r="1451">
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>D17059.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr"/>
+    </row>
+    <row r="1454">
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>D17041.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr"/>
+    </row>
+    <row r="1457">
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr"/>
+    </row>
+    <row r="1458">
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>D17040.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr"/>
+    </row>
+    <row r="1460">
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>D17059.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr"/>
+    </row>
+    <row r="1462">
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>D17040.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr"/>
+    </row>
+    <row r="1464">
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>D17059.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr"/>
+    </row>
+    <row r="1466">
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>M601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr"/>
+    </row>
+    <row r="1468">
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>D17059.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>M17002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>MPS</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr"/>
+    </row>
+    <row r="1471">
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>D17059.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="C1473" t="inlineStr"/>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>UA\G30111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr"/>
+    </row>
+    <row r="1475">
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>D17059.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="C1477" t="inlineStr"/>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>UA\G30112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr"/>
+    </row>
+    <row r="1479">
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>D17059.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="C1481" t="inlineStr"/>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>UA\G30110</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr"/>
+    </row>
+    <row r="1483">
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>D17059.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>D17059.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>ANB</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="C1487" t="inlineStr"/>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>UA\G4402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>MRD</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr"/>
+    </row>
+    <row r="1489">
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>D17059.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="C1491" t="inlineStr"/>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>UA\G1651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr"/>
+    </row>
+    <row r="1493">
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>D17059.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>K0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="C1495" t="inlineStr"/>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>UA\G1651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="C1496" t="inlineStr">
         <is>
           <t>END</t>
         </is>

--- a/motion_mecro_qd77_result2.xlsx
+++ b/motion_mecro_qd77_result2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="8235" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-15" yWindow="17880" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Exported" sheetId="1" state="visible" r:id="rId1"/>
@@ -22877,6 +22877,14 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>B1&lt;&gt;C1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>B1=C1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="expression" priority="3" dxfId="1">
       <formula>D1&lt;&gt;E1</formula>
@@ -22885,14 +22893,6 @@
       <formula>D1=E1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>B1&lt;&gt;C1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>B1=C1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>